--- a/CL_groupe-22-release-planning-final.xlsx
+++ b/CL_groupe-22-release-planning-final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ulysse\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ulysse\Documents\APOCALIPSSI 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135AA2A9-BDCE-4C84-8EE8-F6F17ABBA31F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_D3B6026E05EA87252EBE838CD93AA4440836D92F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Couverture" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="04_Auto-évaluation" sheetId="5" r:id="rId5"/>
     <sheet name="05_Écarts_à_valider" sheetId="6" r:id="rId6"/>
     <sheet name="06_Traceabilité_CJ" sheetId="7" r:id="rId7"/>
+    <sheet name="07_Modifications" sheetId="8" r:id="rId8"/>
+    <sheet name="08_Périmètre_Stories" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="402">
   <si>
     <t>A
 APOCAL'IPSSI</t>
@@ -48,17 +50,6 @@
     <t>RELEASE PLANNING</t>
   </si>
   <si>
-    <t>Planning des 7 sprints demi-journée et des 2 releases d'EduTutor IA
-Version intégrant la Customer Journey finale Étudiante + Enseignante</t>
-  </si>
-  <si>
-    <t>MVP étudiant + premier périmètre enseignant Mme Lefèvre</t>
-  </si>
-  <si>
-    <t>Projet EduTutor IA · Édition 2026 · Semaine immersive Scrum
-Équipe 22 · Version v2.1 · Statut : Draft à valider par le PO</t>
-  </si>
-  <si>
     <t>IDENTIFICATION DU DOCUMENT</t>
   </si>
   <si>
@@ -77,100 +68,19 @@
     <t>Sprint concerné</t>
   </si>
   <si>
-    <t>Cadrage / post-perturbation J1</t>
-  </si>
-  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>v2.1</t>
-  </si>
-  <si>
     <t>Date de remise</t>
   </si>
   <si>
-    <t>30/06/2026</t>
-  </si>
-  <si>
     <t>Statut</t>
   </si>
   <si>
-    <t>Draft - en attente de validation PO</t>
-  </si>
-  <si>
-    <t>DÉCISION DE CADRAGE J1 RETENUE POUR CE PLANNING</t>
-  </si>
-  <si>
-    <t>La cible enseignante reste un SHOULD afin de préserver le MVP étudiant. La Customer Journey finale confirme un parcours enseignant progressif : découverte, adoption, usage hebdomadaire, satisfaction/frustration puis fidélisation. La Release 1 couvre l'adoption et le premier usage régulier (création/partage du quiz + consultation des résultats de classe). La Release 2 couvre la détection des étudiants en difficulté et le suivi individuel. L'envoi de conseils personnalisés et l'export Word/PDF restent hors engagement tant qu'ils ne sont pas formalisés dans le Product Backlog.</t>
-  </si>
-  <si>
     <t>HYPOTHÈSES DE CAPACITÉ</t>
   </si>
   <si>
-    <t>Taille équipe</t>
-  </si>
-  <si>
-    <t>personnes</t>
-  </si>
-  <si>
-    <t>À confirmer en équipe : absences, disponibilités réelles, état du code brownfield et capacité consommée par les perturbations techniques. Les SP reflètent la valeur fonctionnelle engagée ; les spikes J2/J3/J4 consomment de la capacité sans être additionnés au scope fonctionnel.</t>
-  </si>
-  <si>
-    <t>Capacité théorique semaine</t>
-  </si>
-  <si>
-    <t>heures-personnes</t>
-  </si>
-  <si>
-    <t>Scope engagé total</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>Release 1</t>
-  </si>
-  <si>
-    <t>Release 2 additionnelle</t>
-  </si>
-  <si>
     <t>SOURCES UTILISÉES</t>
-  </si>
-  <si>
-    <t>Story Map</t>
-  </si>
-  <si>
-    <t>Texte fourni dans la conversation - version après perturbation J1</t>
-  </si>
-  <si>
-    <t>Product Backlog</t>
-  </si>
-  <si>
-    <t>product-backlog.docx</t>
-  </si>
-  <si>
-    <t>Customer Journey</t>
-  </si>
-  <si>
-    <t>customer-journey-final.docx — parcours Léa Martin et Mme Sophie Lefèvre</t>
-  </si>
-  <si>
-    <t>Persona enseignante</t>
-  </si>
-  <si>
-    <t>equipe-22-persona-lefevre-v2.0.md</t>
-  </si>
-  <si>
-    <t>Template</t>
-  </si>
-  <si>
-    <t>release-planning-prof.xlsx (fichier reçu au format PDF, structure reconstruite en XLSX modifiable)</t>
-  </si>
-  <si>
-    <t>RELEASE PLANNING : SEMAINE APOCAL'IPSSI 2026</t>
-  </si>
-  <si>
-    <t>7 sprints × demi-journée + cadrage matinal + soutenance vendredi · Customer Journey finale intégrée · J1/J2/J3/J3-bis/J4 positionnées</t>
   </si>
   <si>
     <t>Sprint</t>
@@ -199,217 +109,7 @@
     <t>Release / Jalon</t>
   </si>
   <si>
-    <t>Cadrage</t>
-  </si>
-  <si>
-    <t>Lundi matin</t>
-  </si>
-  <si>
-    <t>9h00 - 13h30</t>
-  </si>
-  <si>
-    <t>n.c.</t>
-  </si>
-  <si>
-    <t>Finaliser les 7 artefacts ; intégrer J1 ; aligner les deux parcours de la Customer Journey finale avec la Story Map et le Product Backlog.</t>
-  </si>
-  <si>
-    <t>Validation PO + décision J1</t>
-  </si>
-  <si>
-    <t>Sprint 1</t>
-  </si>
-  <si>
-    <t>Lundi PM</t>
-  </si>
-  <si>
-    <t>14h00 - 18h00</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Livrer l'entrée du parcours étudiant : création de compte et import du cours, avec validation du flux d'inscription.</t>
-  </si>
-  <si>
-    <t>US-01 (3) · US-02 (5) = 8 SP</t>
-  </si>
-  <si>
-    <t>Sprint Review 18h</t>
-  </si>
-  <si>
-    <t>Sprint 2</t>
-  </si>
-  <si>
-    <t>Mardi matin</t>
-  </si>
-  <si>
-    <t>9h00 - 12h30</t>
-  </si>
-  <si>
-    <t>8-10</t>
-  </si>
-  <si>
-    <t>Générer 10 QCM depuis le cours ; mesurer la latence perçue identifiée dans la Customer Journey ; lancer le benchmark J2 et préparer l'ADR.</t>
-  </si>
-  <si>
-    <t>US-03 (8) = 8 SP</t>
-  </si>
-  <si>
-    <t>⚡ Perturbation J2 à 10h</t>
-  </si>
-  <si>
-    <t>Sprint 3</t>
-  </si>
-  <si>
-    <t>Mardi PM</t>
-  </si>
-  <si>
-    <t>Faire réaliser le quiz, corriger automatiquement, afficher le score et sécuriser la récupération du compte.</t>
-  </si>
-  <si>
-    <t>US-04 (3) · US-05 (3) · US-07 (3) = 9 SP</t>
-  </si>
-  <si>
-    <t>Sprint 4</t>
-  </si>
-  <si>
-    <t>Mercredi matin</t>
-  </si>
-  <si>
-    <t>Couvrir l'étape d'adoption enseignante : créer un quiz, le partager à la classe et préparer un usage sans installation complexe.</t>
-  </si>
-  <si>
-    <t>US-21 (8) = 8 SP</t>
-  </si>
-  <si>
-    <t>⚡ Perturbation J3 à 10h</t>
-  </si>
-  <si>
-    <t>Sprint 5</t>
-  </si>
-  <si>
-    <t>Mercredi PM</t>
-  </si>
-  <si>
-    <t>Couvrir l'usage régulier : historique étudiant + dashboard de résultats de classe, avec attention au réseau dégradé et aux droits d'accès.</t>
-  </si>
-  <si>
-    <t>US-06 (3) · US-22 (5) = 8 SP</t>
-  </si>
-  <si>
-    <t>⚡ J3-bis 14h · RELEASE 1 à 17h45</t>
-  </si>
-  <si>
-    <t>Sprint 6</t>
-  </si>
-  <si>
-    <t>Jeudi matin</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Couvrir la satisfaction enseignante : trier les scores et détecter les étudiants sous 5/10 sur 2 quiz consécutifs ; absorber J4.</t>
-  </si>
-  <si>
-    <t>US-J1-01 provisoire (5) = 5 SP</t>
-  </si>
-  <si>
-    <t>⚡ Perturbation J4 à 10h</t>
-  </si>
-  <si>
-    <t>Sprint 7</t>
-  </si>
-  <si>
-    <t>Jeudi PM</t>
-  </si>
-  <si>
-    <t>14h00 - 17h00</t>
-  </si>
-  <si>
-    <t>6-8</t>
-  </si>
-  <si>
-    <t>Consolider le suivi individuel et la fiabilité du dashboard ; finaliser la Release 2. Conseil personnalisé et export restent des stretch goals non engagés.</t>
-  </si>
-  <si>
-    <t>US-J1-02 provisoire (5) = 5 SP</t>
-  </si>
-  <si>
-    <t>RELEASE 2 à 17h</t>
-  </si>
-  <si>
-    <t>Soutenance</t>
-  </si>
-  <si>
-    <t>Vendredi</t>
-  </si>
-  <si>
-    <t>Selon planning</t>
-  </si>
-  <si>
-    <t>Pitch 15 min + démo des parcours Léa et Mme Lefèvre + résultats des perturbations + retour réflexif + Q/R jury.</t>
-  </si>
-  <si>
-    <t>Soutenance + délibération</t>
-  </si>
-  <si>
     <t>SYNTHÈSE DU PÉRIMÈTRE ENGAGÉ</t>
-  </si>
-  <si>
-    <t>Indicateur</t>
-  </si>
-  <si>
-    <t>Valeur</t>
-  </si>
-  <si>
-    <t>Unité</t>
-  </si>
-  <si>
-    <t>Lecture</t>
-  </si>
-  <si>
-    <t>Le planning trace désormais les deux parcours finaux. Les actions « exporter un quiz en Word/PDF » et « envoyer un conseil ciblé » apparaissent dans la Customer Journey enseignante, mais ne sont pas engagées : elles doivent d'abord devenir des User Stories officielles avec priorité, critères d'acceptation et estimation. Les stories J1 de détection et de progression restent provisoires jusqu'à régularisation du Backlog.</t>
-  </si>
-  <si>
-    <t>Capacité totale</t>
-  </si>
-  <si>
-    <t>h-pers</t>
-  </si>
-  <si>
-    <t>Hypothèse 7 personnes sans absence</t>
-  </si>
-  <si>
-    <t>SP Release 1</t>
-  </si>
-  <si>
-    <t>MVP étudiant + premier flux enseignant</t>
-  </si>
-  <si>
-    <t>SP Release 2</t>
-  </si>
-  <si>
-    <t>Détection + progression enseignant</t>
-  </si>
-  <si>
-    <t>SP total engagés</t>
-  </si>
-  <si>
-    <t>Dans la cible du template (~50-60 SP)</t>
-  </si>
-  <si>
-    <t>Marge fonctionnelle</t>
-  </si>
-  <si>
-    <t>60 SP - scope engagé</t>
-  </si>
-  <si>
-    <t>BURNUP GLOBAL : SEMAINE APOCAL'IPSSI 2026</t>
-  </si>
-  <si>
-    <t>SP livrés cumulés vs scope engagé post-J1. La colonne « Réel » est à renseigner après chaque Sprint Review.</t>
   </si>
   <si>
     <t>Fin de sprint</t>
@@ -430,6 +130,356 @@
     <t>Scope total</t>
   </si>
   <si>
+    <t>GRILLE D'AUTO-ÉVALUATION</t>
+  </si>
+  <si>
+    <t>Critère qualité</t>
+  </si>
+  <si>
+    <t>Auto-évaluation</t>
+  </si>
+  <si>
+    <t>Commentaire / preuve</t>
+  </si>
+  <si>
+    <t>Action restante</t>
+  </si>
+  <si>
+    <t>ÉCARTS À RÉGULARISER AVANT VALIDATION PO</t>
+  </si>
+  <si>
+    <t>Priorité</t>
+  </si>
+  <si>
+    <t>Écart constaté</t>
+  </si>
+  <si>
+    <t>Pourquoi c'est important</t>
+  </si>
+  <si>
+    <t>Action attendue</t>
+  </si>
+  <si>
+    <t>Impact planning</t>
+  </si>
+  <si>
+    <t>TRAÇABILITÉ CUSTOMER JOURNEY → RELEASE PLANNING</t>
+  </si>
+  <si>
+    <t>Vérification que les étapes des parcours finaux de Léa Martin et Mme Sophie Lefèvre sont couvertes, reportées ou explicitement hors engagement.</t>
+  </si>
+  <si>
+    <t>Persona</t>
+  </si>
+  <si>
+    <t>Étape du parcours</t>
+  </si>
+  <si>
+    <t>Besoin / action clé</t>
+  </si>
+  <si>
+    <t>Story / périmètre</t>
+  </si>
+  <si>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>Planning des 7 sprints et des 2 releases d'EduTutor IA
+Version consolidée après les perturbations J3 Sécurité et J3-bis RGPD</t>
+  </si>
+  <si>
+    <t>Release 1 : MVP étudiant sécurisé et conforme · Release 2 : parcours enseignant prioritaire</t>
+  </si>
+  <si>
+    <t>Projet EduTutor IA · Édition 2026 · Semaine immersive Scrum
+Équipe 22 · Version v3.0 · Statut : Draft à valider par le PO</t>
+  </si>
+  <si>
+    <t>Cadrage / post-perturbations J3 et J3-bis</t>
+  </si>
+  <si>
+    <t>v3.0</t>
+  </si>
+  <si>
+    <t>01/07/2026</t>
+  </si>
+  <si>
+    <t>Draft - en attente de validation PO</t>
+  </si>
+  <si>
+    <t>DÉCISION DE REPLANIFICATION POST-J3 / J3-BIS</t>
+  </si>
+  <si>
+    <t>Le Release Planning suit le Product Backlog le plus récent : les stories J3 de sécurité (US-24 à US-26) et J3-bis RGPD (US-12 et US-27) sont intégrées à la Release 1. Les fonctionnalités enseignantes US-21, US-22 et US-23 restent prioritaires dans le scope global, mais sont déplacées en Release 2 afin de protéger l'échéance du MVP sécurisé et conforme. Les anciennes stories J1 provisoires de détection et de progression ne sont plus comptées tant qu'elles ne sont pas officialisées dans le Backlog.</t>
+  </si>
+  <si>
+    <t>Taille équipe</t>
+  </si>
+  <si>
+    <t>personnes</t>
+  </si>
+  <si>
+    <t>Hypothèse de planification : les stories techniques J3/J3-bis sont comptées séparément car elles disposent désormais d'identifiants et de Story Points propres dans le Product Backlog. Les estimations restent à confirmer en Planning Poker. Les Sprints 4 et 6 portent 13 SP : ce sont les deux principaux points de vigilance.</t>
+  </si>
+  <si>
+    <t>Capacité théorique semaine</t>
+  </si>
+  <si>
+    <t>heures-personnes</t>
+  </si>
+  <si>
+    <t>Scope engagé total</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>Release 1</t>
+  </si>
+  <si>
+    <t>Release 2 additionnelle</t>
+  </si>
+  <si>
+    <t>Story Map</t>
+  </si>
+  <si>
+    <t>Version post-J1 fournie par l'équipe</t>
+  </si>
+  <si>
+    <t>Product Backlog</t>
+  </si>
+  <si>
+    <t>product-backlog + perturbations j3.docx — US-01 à US-27</t>
+  </si>
+  <si>
+    <t>Customer Journey</t>
+  </si>
+  <si>
+    <t>customer-journey-final.docx — Léa Martin et Mme Sophie Lefèvre</t>
+  </si>
+  <si>
+    <t>Persona enseignante</t>
+  </si>
+  <si>
+    <t>equipe-22-persona-lefevre-v2.0.md</t>
+  </si>
+  <si>
+    <t>Release Planning</t>
+  </si>
+  <si>
+    <t>Version v3.0 consolidée J3 / J3-bis</t>
+  </si>
+  <si>
+    <t>RELEASE PLANNING : VERSION POST-J3 / J3-BIS</t>
+  </si>
+  <si>
+    <t>7 sprints × demi-journée · Release 1 sécurisée et conforme en fin de Sprint 5 · Release 2 enseignante en fin de Sprint 7</t>
+  </si>
+  <si>
+    <t>Cadrage</t>
+  </si>
+  <si>
+    <t>Lundi matin</t>
+  </si>
+  <si>
+    <t>9h00 - 13h30</t>
+  </si>
+  <si>
+    <t>n.c.</t>
+  </si>
+  <si>
+    <t>Aligner Story Map, Product Backlog, Customer Journey et Release Planning ; intégrer J1 ; poser le cadre des perturbations.</t>
+  </si>
+  <si>
+    <t>Validation PO + décision J1</t>
+  </si>
+  <si>
+    <t>Sprint 1</t>
+  </si>
+  <si>
+    <t>Lundi PM</t>
+  </si>
+  <si>
+    <t>14h00 - 18h00</t>
+  </si>
+  <si>
+    <t>8-10</t>
+  </si>
+  <si>
+    <t>Livrer l'entrée du parcours étudiant : création de compte et import du cours.</t>
+  </si>
+  <si>
+    <t>US-01 (3) · US-02 (5) = 8 SP</t>
+  </si>
+  <si>
+    <t>Sprint Review 18h</t>
+  </si>
+  <si>
+    <t>Sprint 2</t>
+  </si>
+  <si>
+    <t>Mardi matin</t>
+  </si>
+  <si>
+    <t>9h00 - 12h30</t>
+  </si>
+  <si>
+    <t>Générer 10 QCM depuis le cours et mesurer la latence avec le benchmark J2.</t>
+  </si>
+  <si>
+    <t>US-03 (8) = 8 SP</t>
+  </si>
+  <si>
+    <t>⚡ Perturbation J2 à 10h</t>
+  </si>
+  <si>
+    <t>Sprint 3</t>
+  </si>
+  <si>
+    <t>Mardi PM</t>
+  </si>
+  <si>
+    <t>Permettre la soumission du quiz, la correction, l'affichage du score et l'historique étudiant.</t>
+  </si>
+  <si>
+    <t>US-04 (3) · US-05 (3) · US-06 (3) = 9 SP</t>
+  </si>
+  <si>
+    <t>Sprint 4</t>
+  </si>
+  <si>
+    <t>Mercredi matin</t>
+  </si>
+  <si>
+    <t>12-13</t>
+  </si>
+  <si>
+    <t>Corriger la vulnérabilité J3 : isoler le contenu du cours, valider les sorties et automatiser les tests adversariaux.</t>
+  </si>
+  <si>
+    <t>US-24 (5) · US-25 (3) · US-26 (5) = 13 SP</t>
+  </si>
+  <si>
+    <t>⚡ Perturbation J3 à 10h</t>
+  </si>
+  <si>
+    <t>Sprint 5</t>
+  </si>
+  <si>
+    <t>Mercredi PM</t>
+  </si>
+  <si>
+    <t>Rendre l'export RGPD utilisable et traçable : JSON/CSV, téléchargement et audit des demandes SAR.</t>
+  </si>
+  <si>
+    <t>US-12 (5) · US-27 (3) = 8 SP</t>
+  </si>
+  <si>
+    <t>⚡ J3-bis 14h · RELEASE 1 = 46 SP</t>
+  </si>
+  <si>
+    <t>Sprint 6</t>
+  </si>
+  <si>
+    <t>Jeudi matin</t>
+  </si>
+  <si>
+    <t>Livrer le premier parcours enseignant prioritaire : créer, partager un quiz et consulter les résultats de classe.</t>
+  </si>
+  <si>
+    <t>US-21 (8) · US-22 (5) = 13 SP</t>
+  </si>
+  <si>
+    <t>⚡ Perturbation J4 à 10h</t>
+  </si>
+  <si>
+    <t>Sprint 7</t>
+  </si>
+  <si>
+    <t>Jeudi PM</t>
+  </si>
+  <si>
+    <t>14h00 - 17h00</t>
+  </si>
+  <si>
+    <t>Finaliser le parcours enseignant avec la correction automatique et stabiliser la Release 2.</t>
+  </si>
+  <si>
+    <t>US-23 (8) = 8 SP</t>
+  </si>
+  <si>
+    <t>RELEASE 2 = 67 SP cumulés</t>
+  </si>
+  <si>
+    <t>Soutenance</t>
+  </si>
+  <si>
+    <t>Vendredi</t>
+  </si>
+  <si>
+    <t>Selon planning</t>
+  </si>
+  <si>
+    <t>Pitch, démonstration du MVP sécurisé/RGPD et du parcours enseignant, retour sur les perturbations et Q/R.</t>
+  </si>
+  <si>
+    <t>Soutenance + délibération</t>
+  </si>
+  <si>
+    <t>Indicateur</t>
+  </si>
+  <si>
+    <t>Valeur</t>
+  </si>
+  <si>
+    <t>Unité</t>
+  </si>
+  <si>
+    <t>Lecture</t>
+  </si>
+  <si>
+    <t>Arbitrage appliqué : la Release 1 est recentrée sur le MVP étudiant, la sécurité et le RGPD. La cible enseignante est considérée comme prioritaire dans le scope global conformément au Backlog, mais elle est livrée en Release 2. Les stories J1 non numérotées ne sont pas incluses dans les 67 SP.</t>
+  </si>
+  <si>
+    <t>Capacité totale</t>
+  </si>
+  <si>
+    <t>h-pers</t>
+  </si>
+  <si>
+    <t>Hypothèse 7 personnes sans absence</t>
+  </si>
+  <si>
+    <t>SP Release 1</t>
+  </si>
+  <si>
+    <t>MVP étudiant + sécurité J3 + RGPD J3-bis</t>
+  </si>
+  <si>
+    <t>SP Release 2</t>
+  </si>
+  <si>
+    <t>Parcours enseignant US-21 à US-23</t>
+  </si>
+  <si>
+    <t>SP total engagés</t>
+  </si>
+  <si>
+    <t>Scope consolidé des stories planifiées</t>
+  </si>
+  <si>
+    <t>Écart vs cible 60 SP</t>
+  </si>
+  <si>
+    <t>Surcapacité à surveiller</t>
+  </si>
+  <si>
+    <t>BURNUP GLOBAL : POST-J3 / J3-BIS</t>
+  </si>
+  <si>
+    <t>SP livrés cumulés vs scope consolidé de 67 SP. La colonne « Réel » reste à renseigner après chaque Sprint Review.</t>
+  </si>
+  <si>
     <t>Sprint 0</t>
   </si>
   <si>
@@ -457,22 +507,7 @@
     <t>Jeu 17h</t>
   </si>
   <si>
-    <t>Lecture : la trajectoire idéale atteint 41 SP à la fin du Sprint 5 (Release 1) et 51 SP à la fin du Sprint 7 (Release 2). Toute hausse liée à une perturbation doit être reportée dans « Scope total » ; toute baisse de vélocité doit apparaître dans « Réel ».</t>
-  </si>
-  <si>
-    <t>GRILLE D'AUTO-ÉVALUATION</t>
-  </si>
-  <si>
-    <t>Critère qualité</t>
-  </si>
-  <si>
-    <t>Auto-évaluation</t>
-  </si>
-  <si>
-    <t>Commentaire / preuve</t>
-  </si>
-  <si>
-    <t>Action restante</t>
+    <t>Lecture : la trajectoire atteint 46 SP à la fin du Sprint 5 (Release 1) et 67 SP à la fin du Sprint 7 (Release 2). Les Sprints 4 et 6 sont les plus chargés avec 13 SP.</t>
   </si>
   <si>
     <t>Les 7 sprints sont planifiés avec jour, horaires et capacité chiffrée.</t>
@@ -484,67 +519,67 @@
     <t>Feuille 02_Release_Planning</t>
   </si>
   <si>
-    <t>La taille de l'équipe est explicite (7 personnes).</t>
-  </si>
-  <si>
-    <t>Feuille 01_Identification</t>
-  </si>
-  <si>
-    <t>Confirmer les absences.</t>
-  </si>
-  <si>
-    <t>Chaque sprint a un objectif clair, mesurable et démontrable.</t>
-  </si>
-  <si>
-    <t>Objectifs décrits sprint par sprint.</t>
-  </si>
-  <si>
-    <t>Les parcours Léa Martin et Mme Lefèvre de la Customer Journey finale sont tracés dans les releases.</t>
-  </si>
-  <si>
-    <t>Feuilles 02 et 06.</t>
-  </si>
-  <si>
-    <t>Chaque sprint liste au moins une story engagée.</t>
+    <t>Le scope J3 et J3-bis est traduit en User Stories planifiées.</t>
+  </si>
+  <si>
+    <t>US-12 et US-24 à US-27 sont positionnées.</t>
+  </si>
+  <si>
+    <t>La Release 1 est recentrée sur le MVP étudiant sécurisé et conforme.</t>
+  </si>
+  <si>
+    <t>46 SP cumulés en fin de S5.</t>
+  </si>
+  <si>
+    <t>La Release 2 couvre le parcours enseignant prioritaire.</t>
+  </si>
+  <si>
+    <t>US-21, US-22 et US-23 en S6/S7.</t>
+  </si>
+  <si>
+    <t>Le Burnup est recalculé sur le nouveau scope.</t>
+  </si>
+  <si>
+    <t>Scope consolidé = 67 SP.</t>
+  </si>
+  <si>
+    <t>Renseigner les SP réels après chaque review.</t>
+  </si>
+  <si>
+    <t>Les parcours Léa Martin et Mme Lefèvre restent traçables.</t>
+  </si>
+  <si>
+    <t>Feuille 06_Traceabilité_CJ.</t>
+  </si>
+  <si>
+    <t>Les stories J1 provisoires non présentes au Backlog ont été retirées du scope engagé.</t>
+  </si>
+  <si>
+    <t>Elles restent dans les écarts à régulariser.</t>
+  </si>
+  <si>
+    <t>Les incohérences du Product Backlog sont identifiées.</t>
+  </si>
+  <si>
+    <t>Feuille 05_Écarts_à_valider.</t>
+  </si>
+  <si>
+    <t>Faire corriger le Backlog source.</t>
+  </si>
+  <si>
+    <t>La charge des sprints est réaliste.</t>
   </si>
   <si>
     <t>Partiel</t>
   </si>
   <si>
-    <t>S6/S7 utilisent des IDs provisoires J1.</t>
-  </si>
-  <si>
-    <t>Créer les stories officielles dans le backlog.</t>
-  </si>
-  <si>
-    <t>La Release 1 est positionnée à la fin du Sprint 5.</t>
-  </si>
-  <si>
-    <t>41 SP cumulés.</t>
-  </si>
-  <si>
-    <t>La Release 2 est positionnée à la fin du Sprint 7.</t>
-  </si>
-  <si>
-    <t>51 SP cumulés.</t>
-  </si>
-  <si>
-    <t>Les perturbations J1, J2, J3, J3-bis et J4 sont positionnées.</t>
-  </si>
-  <si>
-    <t>J1 au cadrage ; autres dans les jalons.</t>
-  </si>
-  <si>
-    <t>Le Burnup contient un scope initial chiffré.</t>
-  </si>
-  <si>
-    <t>Scope post-J1 = 51 SP.</t>
-  </si>
-  <si>
-    <t>Renseigner le réel après chaque review.</t>
-  </si>
-  <si>
-    <t>Le Release Planning a été co-construit et validé par le PO.</t>
+    <t>S4 et S6 = 13 SP.</t>
+  </si>
+  <si>
+    <t>Valider la capacité en Sprint Planning.</t>
+  </si>
+  <si>
+    <t>Le Release Planning a été validé par le PO.</t>
   </si>
   <si>
     <t>Non</t>
@@ -556,181 +591,133 @@
     <t>Revue équipe + validation PO.</t>
   </si>
   <si>
-    <t>ÉCARTS À RÉGULARISER AVANT VALIDATION PO</t>
-  </si>
-  <si>
-    <t>Priorité</t>
-  </si>
-  <si>
-    <t>Écart constaté</t>
-  </si>
-  <si>
-    <t>Pourquoi c'est important</t>
-  </si>
-  <si>
-    <t>Action attendue</t>
-  </si>
-  <si>
-    <t>Impact planning</t>
-  </si>
-  <si>
     <t>Haute</t>
   </si>
   <si>
-    <t>US-07 est SHOULD dans le Product Backlog, mais la Story Map classe la réinitialisation du mot de passe en MUST.</t>
-  </si>
-  <si>
-    <t>La priorité modifie la Release 1.</t>
-  </si>
-  <si>
-    <t>Faire arbitrer le PO ; ce planning la traite comme MUST.</t>
-  </si>
-  <si>
-    <t>S3 = 9 SP.</t>
-  </si>
-  <si>
-    <t>US-21 et US-23 sont MUST dans le Backlog, alors que le persona et la Story Map recommandent la cible enseignante en SHOULD.</t>
-  </si>
-  <si>
-    <t>Risque de surcharger la Release 1.</t>
-  </si>
-  <si>
-    <t>Aligner MoSCoW dans le Backlog et la note de décision J1.</t>
-  </si>
-  <si>
-    <t>Ce planning ne compte pas US-23 séparément.</t>
-  </si>
-  <si>
-    <t>Les stories de détection des étudiants en difficulté et de suivi individuel n'ont pas d'ID officiel, de SP validés ni de critères d'acceptation.</t>
-  </si>
-  <si>
-    <t>Le Release Planning exige une traçabilité US-XX.</t>
-  </si>
-  <si>
-    <t>Créer US-J1-01 et US-J1-02 ; confirmer 5 SP chacune.</t>
-  </si>
-  <si>
-    <t>S6 et S7 restent provisoires.</t>
-  </si>
-  <si>
-    <t>La Customer Journey finale fixe une règle concrète de décrochage : score &lt; 5/10 sur 2 quiz consécutifs.</t>
-  </si>
-  <si>
-    <t>Cette règle doit devenir testable et non rester seulement narrative.</t>
-  </si>
-  <si>
-    <t>L'ajouter aux critères Given/When/Then de la story de détection.</t>
-  </si>
-  <si>
-    <t>Pas de changement de SP estimé.</t>
+    <t>Le Backlog affiche encore 20/23 stories et 137 SP alors qu'il contient US-01 à US-27.</t>
+  </si>
+  <si>
+    <t>Les totaux source sont obsolètes.</t>
+  </si>
+  <si>
+    <t>Corriger les métadonnées du Backlog et recalculer ses totaux.</t>
+  </si>
+  <si>
+    <t>Le Release Planning utilise uniquement les stories planifiées.</t>
+  </si>
+  <si>
+    <t>La Story Map/persona positionne l'enseignante en SHOULD alors que le Backlog marque US-21 et US-23 en MUST.</t>
+  </si>
+  <si>
+    <t>Les artefacts ne racontent pas la même priorité.</t>
+  </si>
+  <si>
+    <t>Aligner Story Map, persona et note MoSCoW sur la décision PO.</t>
+  </si>
+  <si>
+    <t>Le planning suit le Backlog et livre la prof en Release 2.</t>
+  </si>
+  <si>
+    <t>US-03 intègre déjà des critères de sécurité proches de US-24 et US-25.</t>
+  </si>
+  <si>
+    <t>Risque de double comptage fonctionnel.</t>
+  </si>
+  <si>
+    <t>Conserver US-24/25 comme incréments J3 distincts ou réestimer US-03.</t>
+  </si>
+  <si>
+    <t>67 SP retenus provisoirement.</t>
+  </si>
+  <si>
+    <t>US-23 recouvre en partie la correction automatique déjà réalisée par US-04/US-05.</t>
+  </si>
+  <si>
+    <t>Risque de dupliquer l'effort.</t>
+  </si>
+  <si>
+    <t>Réutiliser le moteur existant et confirmer l'estimation de 8 SP.</t>
+  </si>
+  <si>
+    <t>Peut réduire la charge du Sprint 7.</t>
   </si>
   <si>
     <t>Moyenne</t>
   </si>
   <si>
-    <t>Le mécanisme de classe (création, rattachement des 28 étudiants et droits d'accès) n'est pas complètement décrit.</t>
-  </si>
-  <si>
-    <t>US-22 dépend d'une relation enseignant-classe-étudiant et d'autorisations fiables.</t>
-  </si>
-  <si>
-    <t>Ajouter dépendances, modèle de données et critères d'autorisation.</t>
-  </si>
-  <si>
-    <t>Peut augmenter le scope de 3 à 8 SP.</t>
-  </si>
-  <si>
-    <t>La Customer Journey enseignante inclut l'export Word/PDF, mais cette capacité n'est pas formalisée dans le Backlog.</t>
-  </si>
-  <si>
-    <t>Une action du parcours ne doit pas apparaître implicitement comme engagée.</t>
-  </si>
-  <si>
-    <t>Créer une story COULD ou déclarer explicitement l'export hors scope.</t>
-  </si>
-  <si>
-    <t>Non engagé dans les 51 SP.</t>
-  </si>
-  <si>
-    <t>La Customer Journey enseignante inclut l'envoi de conseils ciblés ; la Story Map le classe COULD.</t>
-  </si>
-  <si>
-    <t>La fidélisation est décrite, mais pas couverte par le scope engagé.</t>
-  </si>
-  <si>
-    <t>Créer une story officielle et la conserver en stretch goal Release 2.</t>
-  </si>
-  <si>
-    <t>Le réseau 4G partagé et la tolérance quasi nulle aux pannes sont des exigences non fonctionnelles.</t>
-  </si>
-  <si>
-    <t>Le dashboard peut être fonctionnel mais inutilisable en classe s'il est lent.</t>
-  </si>
-  <si>
-    <t>Ajouter seuils de performance, loader, gestion d'erreur et test réseau dégradé.</t>
-  </si>
-  <si>
-    <t>Réserver de la capacité technique en S5/S7.</t>
-  </si>
-  <si>
-    <t>US-23 « correction automatique enseignant » recouvre largement US-04/US-05.</t>
-  </si>
-  <si>
-    <t>Risque de double comptage.</t>
-  </si>
-  <si>
-    <t>Supprimer, fusionner ou réécrire US-23.</t>
-  </si>
-  <si>
-    <t>Non planifiée séparément.</t>
-  </si>
-  <si>
-    <t>Les travaux J2/J3/J4 ne sont pas estimés dans le Backlog.</t>
-  </si>
-  <si>
-    <t>Ils consomment de la capacité réelle.</t>
-  </si>
-  <si>
-    <t>Créer des spikes/tâches techniques et réserver la capacité.</t>
-  </si>
-  <si>
-    <t>Réduit la marge sans augmenter les SP fonctionnels.</t>
+    <t>US-27 n'a pas de critères Given/When/Then détaillés dans la version fournie.</t>
+  </si>
+  <si>
+    <t>L'audit SAR doit être testable.</t>
+  </si>
+  <si>
+    <t>Ajouter utilisateur, date, statut, date de réponse et hash d'export.</t>
+  </si>
+  <si>
+    <t>S5 reste à 8 SP sous réserve.</t>
+  </si>
+  <si>
+    <t>La règle de détection des décrocheurs (&lt;5/10 sur 2 quiz) n'a toujours pas de story officielle.</t>
+  </si>
+  <si>
+    <t>Le besoin J1 n'est pas traçable.</t>
+  </si>
+  <si>
+    <t>Créer une US dédiée ou l'intégrer à US-22.</t>
+  </si>
+  <si>
+    <t>Non incluse dans les 67 SP.</t>
+  </si>
+  <si>
+    <t>Le réseau dégradé et la disponibilité du dashboard restent des exigences non fonctionnelles.</t>
+  </si>
+  <si>
+    <t>Risque d'échec en classe.</t>
+  </si>
+  <si>
+    <t>Ajouter tests de performance, loader et gestion d'erreur.</t>
+  </si>
+  <si>
+    <t>À réserver dans S6/S7.</t>
+  </si>
+  <si>
+    <t>US-07 est SHOULD/S6 dans le Backlog mais était auparavant traitée comme MUST/S3.</t>
+  </si>
+  <si>
+    <t>Le périmètre a changé.</t>
+  </si>
+  <si>
+    <t>Confirmer son report hors scope engagé.</t>
+  </si>
+  <si>
+    <t>US-07 retirée des 67 SP.</t>
+  </si>
+  <si>
+    <t>Les Sprints 4 et 6 portent chacun 13 SP.</t>
+  </si>
+  <si>
+    <t>Risque de dépassement de vélocité.</t>
+  </si>
+  <si>
+    <t>Découper les tâches et réarbitrer au Sprint Planning.</t>
+  </si>
+  <si>
+    <t>Point de vigilance principal.</t>
   </si>
   <si>
     <t>Basse</t>
   </si>
   <si>
-    <t>La capacité théorique suppose 7 personnes disponibles sur toute la semaine.</t>
+    <t>La capacité suppose 7 personnes présentes sur toute la semaine.</t>
   </si>
   <si>
     <t>Toute absence réduit les 203 h-pers.</t>
   </si>
   <si>
-    <t>Confirmer les disponibilités au Daily / Sprint Planning.</t>
-  </si>
-  <si>
-    <t>Replanification si écart significatif.</t>
-  </si>
-  <si>
-    <t>TRAÇABILITÉ CUSTOMER JOURNEY → RELEASE PLANNING</t>
-  </si>
-  <si>
-    <t>Vérification que les étapes des parcours finaux de Léa Martin et Mme Sophie Lefèvre sont couvertes, reportées ou explicitement hors engagement.</t>
-  </si>
-  <si>
-    <t>Persona</t>
-  </si>
-  <si>
-    <t>Étape du parcours</t>
-  </si>
-  <si>
-    <t>Besoin / action clé</t>
-  </si>
-  <si>
-    <t>Story / périmètre</t>
-  </si>
-  <si>
-    <t>Observation</t>
+    <t>Confirmer les disponibilités au Daily.</t>
+  </si>
+  <si>
+    <t>Replanification si besoin.</t>
   </si>
   <si>
     <t>Léa Martin</t>
@@ -751,22 +738,22 @@
     <t>Engagé</t>
   </si>
   <si>
-    <t>Première entrée dans le produit.</t>
+    <t>Entrée dans le produit.</t>
   </si>
   <si>
     <t>Première utilisation</t>
   </si>
   <si>
-    <t>Importer PDF ≤ 5 Mo ou texte ≥ 200 caractères</t>
+    <t>Importer PDF ou texte</t>
   </si>
   <si>
     <t>US-02</t>
   </si>
   <si>
-    <t>Précondition de la génération.</t>
-  </si>
-  <si>
-    <t>Générer 10 QCM depuis son propre cours</t>
+    <t>Précondition du quiz.</t>
+  </si>
+  <si>
+    <t>Générer 10 QCM depuis son cours</t>
   </si>
   <si>
     <t>US-03</t>
@@ -778,7 +765,52 @@
     <t>Latence traitée par J2.</t>
   </si>
   <si>
-    <t>Répondre, soumettre et voir les corrections</t>
+    <t>Sécurité</t>
+  </si>
+  <si>
+    <t>Ignorer les instructions malveillantes du cours</t>
+  </si>
+  <si>
+    <t>US-24</t>
+  </si>
+  <si>
+    <t>S4</t>
+  </si>
+  <si>
+    <t>Patch J3.</t>
+  </si>
+  <si>
+    <t>Tous personas</t>
+  </si>
+  <si>
+    <t>Fiabilité</t>
+  </si>
+  <si>
+    <t>Valider automatiquement le quiz avant affichage</t>
+  </si>
+  <si>
+    <t>US-25</t>
+  </si>
+  <si>
+    <t>Format et cohérence.</t>
+  </si>
+  <si>
+    <t>Équipe de dev</t>
+  </si>
+  <si>
+    <t>Sécurité CI</t>
+  </si>
+  <si>
+    <t>Exécuter les tests adversariaux sur push/PR</t>
+  </si>
+  <si>
+    <t>US-26</t>
+  </si>
+  <si>
+    <t>Non-régression.</t>
+  </si>
+  <si>
+    <t>Soumettre, corriger et voir le score</t>
   </si>
   <si>
     <t>US-04 / US-05</t>
@@ -787,157 +819,442 @@
     <t>S3</t>
   </si>
   <si>
-    <t>Cœur du MVP étudiant.</t>
+    <t>Cœur du MVP.</t>
   </si>
   <si>
     <t>Utilisation régulière</t>
   </si>
   <si>
-    <t>Consulter l'historique des quiz</t>
+    <t>Consulter l'historique</t>
   </si>
   <si>
     <t>US-06</t>
   </si>
   <si>
+    <t>Progression minimale.</t>
+  </si>
+  <si>
+    <t>Gestion du compte</t>
+  </si>
+  <si>
+    <t>Exporter ses données en JSON/CSV</t>
+  </si>
+  <si>
+    <t>US-12</t>
+  </si>
+  <si>
     <t>S5</t>
   </si>
   <si>
-    <t>Progression minimale.</t>
-  </si>
-  <si>
-    <t>Dashboard avancé et révision ciblée</t>
-  </si>
-  <si>
-    <t>US-11 / US-16</t>
+    <t>Droit d'accès RGPD.</t>
+  </si>
+  <si>
+    <t>Administrateur</t>
+  </si>
+  <si>
+    <t>Conformité</t>
+  </si>
+  <si>
+    <t>Tracer les demandes SAR</t>
+  </si>
+  <si>
+    <t>US-27</t>
+  </si>
+  <si>
+    <t>Audit trail RGPD.</t>
+  </si>
+  <si>
+    <t>Mme Lefèvre</t>
+  </si>
+  <si>
+    <t>Adoption</t>
+  </si>
+  <si>
+    <t>Créer et partager un quiz</t>
+  </si>
+  <si>
+    <t>US-21</t>
+  </si>
+  <si>
+    <t>S6</t>
+  </si>
+  <si>
+    <t>Cible enseignante prioritaire.</t>
+  </si>
+  <si>
+    <t>Utilisation hebdomadaire</t>
+  </si>
+  <si>
+    <t>Voir les résultats de classe</t>
+  </si>
+  <si>
+    <t>US-22</t>
+  </si>
+  <si>
+    <t>Dashboard de classe.</t>
+  </si>
+  <si>
+    <t>Correction</t>
+  </si>
+  <si>
+    <t>Corriger automatiquement les réponses</t>
+  </si>
+  <si>
+    <t>US-23</t>
+  </si>
+  <si>
+    <t>S7</t>
+  </si>
+  <si>
+    <t>Réutilisation attendue de US-04/05.</t>
+  </si>
+  <si>
+    <t>Satisfaction</t>
+  </si>
+  <si>
+    <t>Repérer &lt;5/10 sur 2 quiz</t>
+  </si>
+  <si>
+    <t>Story non créée</t>
   </si>
   <si>
     <t>Après R2</t>
   </si>
   <si>
-    <t>Reporté</t>
-  </si>
-  <si>
-    <t>Non inclus dans les 51 SP.</t>
-  </si>
-  <si>
-    <t>Mme Lefèvre</t>
-  </si>
-  <si>
-    <t>Découverte</t>
-  </si>
-  <si>
-    <t>Comprendre la valeur, la simplicité et la conformité RGPD</t>
-  </si>
-  <si>
-    <t>NFR / documentation</t>
-  </si>
-  <si>
-    <t>Cadrage + S5</t>
-  </si>
-  <si>
-    <t>Preuves RGPD à rendre visibles.</t>
-  </si>
-  <si>
-    <t>Adoption</t>
-  </si>
-  <si>
-    <t>Créer et partager un quiz à la classe</t>
-  </si>
-  <si>
-    <t>US-21</t>
-  </si>
-  <si>
-    <t>S4</t>
-  </si>
-  <si>
-    <t>Premier usage enseignant.</t>
-  </si>
-  <si>
-    <t>Utilisation hebdomadaire</t>
-  </si>
-  <si>
-    <t>Voir les résultats et trier les 28 étudiants</t>
-  </si>
-  <si>
-    <t>US-22</t>
-  </si>
-  <si>
-    <t>Dashboard de classe.</t>
-  </si>
-  <si>
-    <t>Satisfaction</t>
-  </si>
-  <si>
-    <t>Repérer &lt;5/10 sur 2 quiz consécutifs</t>
-  </si>
-  <si>
-    <t>US-J1-01 provisoire</t>
-  </si>
-  <si>
-    <t>S6</t>
-  </si>
-  <si>
-    <t>Engagé provisoire</t>
-  </si>
-  <si>
-    <t>Critères à officialiser.</t>
-  </si>
-  <si>
-    <t>Fidélisation</t>
-  </si>
-  <si>
-    <t>Suivre la progression individuelle</t>
-  </si>
-  <si>
-    <t>US-J1-02 provisoire</t>
-  </si>
-  <si>
-    <t>S7</t>
-  </si>
-  <si>
-    <t>Envoyer un conseil personnalisé</t>
-  </si>
-  <si>
-    <t>COULD non numéroté</t>
-  </si>
-  <si>
-    <t>Après R2 / stretch</t>
-  </si>
-  <si>
     <t>Non engagé</t>
   </si>
   <si>
-    <t>Créer une US officielle.</t>
-  </si>
-  <si>
-    <t>Exporter le quiz en Word/PDF</t>
-  </si>
-  <si>
-    <t>Non présent au backlog</t>
-  </si>
-  <si>
-    <t>À arbitrer</t>
-  </si>
-  <si>
-    <t>Créer une US ou déclarer hors scope.</t>
-  </si>
-  <si>
-    <t>Satisfaction / frustration</t>
-  </si>
-  <si>
-    <t>Dashboard utilisable en réseau 4G dégradé</t>
-  </si>
-  <si>
-    <t>NFR performance</t>
-  </si>
-  <si>
-    <t>S5 / S7</t>
-  </si>
-  <si>
-    <t>À intégrer</t>
-  </si>
-  <si>
-    <t>Ajouter seuils et tests.</t>
+    <t>Besoin J1 à officialiser.</t>
+  </si>
+  <si>
+    <t>LISTE DES MODIFICATIONS EFFECTUÉES — VERSION v3.0</t>
+  </si>
+  <si>
+    <t>Synthèse des changements appliqués au Release Planning après analyse du Product Backlog intégrant J3 et J3-bis.</t>
+  </si>
+  <si>
+    <t>Zone modifiée</t>
+  </si>
+  <si>
+    <t>Modification</t>
+  </si>
+  <si>
+    <t>Pourquoi</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Version / couverture</t>
+  </si>
+  <si>
+    <t>Passage en v3.0 post-J3/J3-bis.</t>
+  </si>
+  <si>
+    <t>Tracer la nouvelle baseline.</t>
+  </si>
+  <si>
+    <t>Document identifiable.</t>
+  </si>
+  <si>
+    <t>Fait</t>
+  </si>
+  <si>
+    <t>Décision de scope</t>
+  </si>
+  <si>
+    <t>Release 1 recentrée sur étudiant + sécurité + RGPD.</t>
+  </si>
+  <si>
+    <t>Protéger l'échéance MVP.</t>
+  </si>
+  <si>
+    <t>46 SP en R1.</t>
+  </si>
+  <si>
+    <t>Parcours enseignant</t>
+  </si>
+  <si>
+    <t>US-21 à US-23 déplacées en Release 2.</t>
+  </si>
+  <si>
+    <t>Libérer la capacité pour J3/J3-bis.</t>
+  </si>
+  <si>
+    <t>21 SP en R2.</t>
+  </si>
+  <si>
+    <t>J3 sécurité</t>
+  </si>
+  <si>
+    <t>Ajout US-24, US-25 et US-26 en Sprint 4.</t>
+  </si>
+  <si>
+    <t>Backlog enrichi après prompt injection.</t>
+  </si>
+  <si>
+    <t>+13 SP.</t>
+  </si>
+  <si>
+    <t>J3-bis RGPD</t>
+  </si>
+  <si>
+    <t>Ajout US-12 et US-27 en Sprint 5.</t>
+  </si>
+  <si>
+    <t>Export et audit SAR obligatoires.</t>
+  </si>
+  <si>
+    <t>+8 SP.</t>
+  </si>
+  <si>
+    <t>US-06 déplacée en Sprint 3 ; US-07 retirée du scope.</t>
+  </si>
+  <si>
+    <t>Aligner les priorités du nouveau Backlog.</t>
+  </si>
+  <si>
+    <t>Sprint 3 = 9 SP.</t>
+  </si>
+  <si>
+    <t>Stories J1 provisoires</t>
+  </si>
+  <si>
+    <t>Retrait de US-J1-01/02 du scope engagé.</t>
+  </si>
+  <si>
+    <t>Elles n'existent pas dans le Backlog officiel.</t>
+  </si>
+  <si>
+    <t>-10 SP anciens.</t>
+  </si>
+  <si>
+    <t>Recalcul de 51 SP à 67 SP.</t>
+  </si>
+  <si>
+    <t>Intégration des stories J3/J3-bis et enseignantes.</t>
+  </si>
+  <si>
+    <t>+16 SP nets.</t>
+  </si>
+  <si>
+    <t>Burnup</t>
+  </si>
+  <si>
+    <t>Courbe idéale recalculée : 8/16/25/38/46/59/67.</t>
+  </si>
+  <si>
+    <t>Refléter le nouveau plan.</t>
+  </si>
+  <si>
+    <t>R1 à 46, R2 à 67.</t>
+  </si>
+  <si>
+    <t>Traceabilité</t>
+  </si>
+  <si>
+    <t>Ajout des stories sécurité, RGPD et enseignantes.</t>
+  </si>
+  <si>
+    <t>Relier besoins, backlog et sprints.</t>
+  </si>
+  <si>
+    <t>Couverture complète.</t>
+  </si>
+  <si>
+    <t>Critères actualisés post-J3/J3-bis.</t>
+  </si>
+  <si>
+    <t>Évaluer la nouvelle version.</t>
+  </si>
+  <si>
+    <t>Points de vigilance visibles.</t>
+  </si>
+  <si>
+    <t>Écarts</t>
+  </si>
+  <si>
+    <t>Liste mise à jour avec doublons et incohérences du Backlog.</t>
+  </si>
+  <si>
+    <t>Éviter de masquer les arbitrages restants.</t>
+  </si>
+  <si>
+    <t>Actions PO identifiées.</t>
+  </si>
+  <si>
+    <t>PÉRIMÈTRE DES STORIES ENGAGÉES</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Intitulé court</t>
+  </si>
+  <si>
+    <t>MoSCoW</t>
+  </si>
+  <si>
+    <t>Release</t>
+  </si>
+  <si>
+    <t>Motif de planification</t>
+  </si>
+  <si>
+    <t>Risque / dépendance</t>
+  </si>
+  <si>
+    <t>Créer un compte</t>
+  </si>
+  <si>
+    <t>MUST</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>Entrée du parcours étudiant</t>
+  </si>
+  <si>
+    <t>Email / auth</t>
+  </si>
+  <si>
+    <t>Précondition de génération</t>
+  </si>
+  <si>
+    <t>Extraction contenu</t>
+  </si>
+  <si>
+    <t>Générer 10 QCM</t>
+  </si>
+  <si>
+    <t>Cœur du MVP</t>
+  </si>
+  <si>
+    <t>Latence J2</t>
+  </si>
+  <si>
+    <t>US-04</t>
+  </si>
+  <si>
+    <t>Soumettre et corriger</t>
+  </si>
+  <si>
+    <t>Évaluation de l'étudiant</t>
+  </si>
+  <si>
+    <t>Moteur correction</t>
+  </si>
+  <si>
+    <t>US-05</t>
+  </si>
+  <si>
+    <t>Afficher score et détails</t>
+  </si>
+  <si>
+    <t>Mesure de progression</t>
+  </si>
+  <si>
+    <t>Dépend US-04</t>
+  </si>
+  <si>
+    <t>Progression minimale</t>
+  </si>
+  <si>
+    <t>Persistance</t>
+  </si>
+  <si>
+    <t>Neutraliser prompt injection</t>
+  </si>
+  <si>
+    <t>Correctif J3 bloquant</t>
+  </si>
+  <si>
+    <t>Chevauche US-03</t>
+  </si>
+  <si>
+    <t>Valider le quiz généré</t>
+  </si>
+  <si>
+    <t>Fiabilité post-LLM</t>
+  </si>
+  <si>
+    <t>Schéma de sortie</t>
+  </si>
+  <si>
+    <t>Tests adversariaux en CI</t>
+  </si>
+  <si>
+    <t>SHOULD</t>
+  </si>
+  <si>
+    <t>Non-régression J3</t>
+  </si>
+  <si>
+    <t>Pipeline CI</t>
+  </si>
+  <si>
+    <t>Exporter JSON / CSV</t>
+  </si>
+  <si>
+    <t>Droit d'accès RGPD</t>
+  </si>
+  <si>
+    <t>Isolation utilisateurs</t>
+  </si>
+  <si>
+    <t>Auditer les demandes SAR</t>
+  </si>
+  <si>
+    <t>Traçabilité RGPD</t>
+  </si>
+  <si>
+    <t>Modèle DataRequest</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>Entrée du parcours enseignant</t>
+  </si>
+  <si>
+    <t>Partage classe</t>
+  </si>
+  <si>
+    <t>Suivi enseignant</t>
+  </si>
+  <si>
+    <t>Droits + dashboard</t>
+  </si>
+  <si>
+    <t>Corriger automatiquement</t>
+  </si>
+  <si>
+    <t>Finaliser le parcours enseignant</t>
+  </si>
+  <si>
+    <t>Réutiliser US-04/05</t>
+  </si>
+  <si>
+    <t>US planifiées dans S1 à S7</t>
+  </si>
+  <si>
+    <t>SP MUST</t>
+  </si>
+  <si>
+    <t>Socle obligatoire global</t>
+  </si>
+  <si>
+    <t>SP SHOULD</t>
+  </si>
+  <si>
+    <t>Compliance et valeur d'usage</t>
+  </si>
+  <si>
+    <t>SP total</t>
+  </si>
+  <si>
+    <t>Scope consolidé</t>
   </si>
 </sst>
 </file>
@@ -981,7 +1298,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1021,6 +1338,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF172554"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF6FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1225,7 +1552,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1353,13 +1680,22 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1377,37 +1713,37 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1440,31 +1776,31 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1495,17 +1831,23 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="21">
     <dxf>
       <font>
         <b/>
@@ -1520,55 +1862,11 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FF92400E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF64748B"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF1F5F9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <color rgb="FFDC2626"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF92400E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF16A34A"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDCFCE7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1589,7 +1887,84 @@
         <color rgb="FF92400E"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF64748B"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF1F5F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFDC2626"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF16A34A"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF16A34A"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFEF3C7"/>
         </patternFill>
       </fill>
@@ -1600,7 +1975,7 @@
         <color rgb="FFDC2626"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFEE2E2"/>
         </patternFill>
       </fill>
@@ -1803,16 +2178,16 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1820,7 +2195,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1B26-4497-8FAC-FA292D681DC2}"/>
+              <c16:uniqueId val="{00000000-F942-4E5C-BA60-39F6CC82D910}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1882,16 +2257,16 @@
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>33</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>41</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>51</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1899,7 +2274,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1B26-4497-8FAC-FA292D681DC2}"/>
+              <c16:uniqueId val="{00000001-F942-4E5C-BA60-39F6CC82D910}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1957,7 +2332,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1B26-4497-8FAC-FA292D681DC2}"/>
+              <c16:uniqueId val="{00000002-F942-4E5C-BA60-39F6CC82D910}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2006,28 +2381,28 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>51</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>51</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>51</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>51</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>51</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>51</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>51</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2035,7 +2410,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-1B26-4497-8FAC-FA292D681DC2}"/>
+              <c16:uniqueId val="{00000003-F942-4E5C-BA60-39F6CC82D910}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2330,182 +2705,194 @@
     <row r="1" spans="2:8" ht="21.95" customHeight="1"/>
     <row r="2" spans="2:8" ht="21.95" customHeight="1"/>
     <row r="3" spans="2:8" ht="21.95" customHeight="1">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="4" spans="2:8" ht="21.95" customHeight="1">
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
     </row>
     <row r="5" spans="2:8" ht="21.95" customHeight="1">
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
     </row>
     <row r="6" spans="2:8" ht="21.95" customHeight="1"/>
     <row r="7" spans="2:8" ht="21.95" customHeight="1">
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
     </row>
     <row r="8" spans="2:8" ht="21.95" customHeight="1">
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
     </row>
     <row r="9" spans="2:8" ht="21.95" customHeight="1">
-      <c r="B9" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9" s="48" t="s">
-        <v>2</v>
+      <c r="B9" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="51" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="21.95" customHeight="1">
-      <c r="B10" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" s="48" t="s">
-        <v>2</v>
+      <c r="B10" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="51" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="21.95" customHeight="1"/>
     <row r="12" spans="2:8" ht="21.95" customHeight="1">
-      <c r="B12" s="49" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
+      <c r="B12" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="52" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="13" spans="2:8" ht="21.95" customHeight="1"/>
     <row r="14" spans="2:8" ht="21.95" customHeight="1"/>
     <row r="15" spans="2:8" ht="21.95" customHeight="1">
-      <c r="B15" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="50" t="s">
-        <v>4</v>
+      <c r="B15" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="53" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="21.95" customHeight="1">
-      <c r="B16" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="50" t="s">
-        <v>4</v>
+      <c r="B16" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="53" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="21.95" customHeight="1">
-      <c r="B17" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="G17" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="50" t="s">
-        <v>4</v>
+      <c r="B17" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="53" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="21.95" customHeight="1"/>
@@ -2536,304 +2923,356 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="A1" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="51"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15">
-      <c r="A11" s="52" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
+      <c r="A11" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="54" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="55" t="s">
-        <v>19</v>
+      <c r="A12" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="58" t="s">
-        <v>19</v>
+      <c r="A13" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="61" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="61" t="s">
-        <v>19</v>
+      <c r="A14" s="62" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="64" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15">
-      <c r="A16" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
+      <c r="A16" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
     </row>
     <row r="17" spans="1:8" ht="15">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="B17" s="15">
         <v>7</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="62" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="64"/>
+        <v>55</v>
+      </c>
+      <c r="E17" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="67" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="30">
       <c r="A18" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B18" s="16">
         <v>203</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="65"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="67"/>
+        <v>58</v>
+      </c>
+      <c r="E18" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="70" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="15">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="B19" s="16">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="65"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="67"/>
+        <v>60</v>
+      </c>
+      <c r="E19" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="70" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="15">
       <c r="A20" s="2" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B20" s="16">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="67"/>
+        <v>60</v>
+      </c>
+      <c r="E20" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="70" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="15">
       <c r="A21" s="3" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B21" s="17">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="68"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="70"/>
+        <v>60</v>
+      </c>
+      <c r="E21" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" s="73" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="15">
-      <c r="A23" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
+      <c r="A23" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
     </row>
     <row r="24" spans="1:8" ht="15">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="28.5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="28.5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15">
       <c r="A28" s="3" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2865,464 +3304,494 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="A1" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="55" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="51"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="A2" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="55" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="71" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="71" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="71" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="71" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="71" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="71" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="71" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="71" t="s">
-        <v>42</v>
+      <c r="A3" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="74" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30">
       <c r="A5" s="21" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="72" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="D6" s="19">
         <v>24.5</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="72" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D7" s="25">
         <v>28</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="72" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D8" s="25">
         <v>24.5</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="72" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D9" s="25">
         <v>28</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="72" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D10" s="25">
         <v>24.5</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="72" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D11" s="8">
         <v>28</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="72" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D12" s="25">
         <v>24.5</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="72" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="D13" s="25">
         <v>21</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="72" customHeight="1">
       <c r="A14" s="28" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15">
-      <c r="A16" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
+      <c r="A16" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
     </row>
     <row r="17" spans="1:8" ht="15">
       <c r="A17" s="21" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="F17" s="72" t="s">
-        <v>108</v>
-      </c>
-      <c r="G17" s="73" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="74" t="s">
-        <v>108</v>
+        <v>128</v>
+      </c>
+      <c r="F17" s="75" t="s">
+        <v>129</v>
+      </c>
+      <c r="G17" s="76" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="77" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="57">
       <c r="A18" s="9" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B18" s="31">
         <f>SUM(D6:D13)</f>
         <v>203</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="75" t="s">
-        <v>108</v>
-      </c>
-      <c r="G18" s="76" t="s">
-        <v>108</v>
-      </c>
-      <c r="H18" s="77" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="42.75">
+        <v>132</v>
+      </c>
+      <c r="F18" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="G18" s="79" t="s">
+        <v>129</v>
+      </c>
+      <c r="H18" s="80" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="57">
       <c r="A19" s="11" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B19" s="32">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F19" s="75" t="s">
-        <v>108</v>
-      </c>
-      <c r="G19" s="76" t="s">
-        <v>108</v>
-      </c>
-      <c r="H19" s="77" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="42.75">
+        <v>134</v>
+      </c>
+      <c r="F19" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" s="79" t="s">
+        <v>129</v>
+      </c>
+      <c r="H19" s="80" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="57">
       <c r="A20" s="11" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="B20" s="32">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="75" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" s="76" t="s">
-        <v>108</v>
-      </c>
-      <c r="H20" s="77" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="42.75">
+        <v>136</v>
+      </c>
+      <c r="F20" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="79" t="s">
+        <v>129</v>
+      </c>
+      <c r="H20" s="80" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="57">
       <c r="A21" s="11" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="B21" s="32">
         <f>SUM(B19:B20)</f>
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="F21" s="75" t="s">
-        <v>108</v>
-      </c>
-      <c r="G21" s="76" t="s">
-        <v>108</v>
-      </c>
-      <c r="H21" s="77" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="42.75">
+        <v>138</v>
+      </c>
+      <c r="F21" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="G21" s="79" t="s">
+        <v>129</v>
+      </c>
+      <c r="H21" s="80" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="28.5">
       <c r="A22" s="13" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B22" s="33">
-        <f>60-B21</f>
-        <v>9</v>
+        <f>B21-60</f>
+        <v>7</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F22" s="78" t="s">
-        <v>108</v>
-      </c>
-      <c r="G22" s="79" t="s">
-        <v>108</v>
-      </c>
-      <c r="H22" s="80" t="s">
-        <v>108</v>
+        <v>140</v>
+      </c>
+      <c r="F22" s="81" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" s="82" t="s">
+        <v>129</v>
+      </c>
+      <c r="H22" s="83" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -3349,80 +3818,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
+      <c r="A1" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="55" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="51"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
+      <c r="A2" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="55" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="81" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
+      <c r="A3" s="84" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="84" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="84" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="84" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="84" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3" s="84" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="30">
       <c r="A5" s="21" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="9" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="C6" s="34">
         <v>0</v>
       </c>
       <c r="D6" s="34">
-        <f>C6</f>
         <v>0</v>
       </c>
       <c r="E6" s="35">
         <v>0</v>
       </c>
       <c r="F6" s="36">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="11" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="C7" s="37">
         <v>8</v>
@@ -3433,15 +3933,15 @@
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="39">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="11" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="C8" s="37">
         <v>8</v>
@@ -3452,15 +3952,15 @@
       </c>
       <c r="E8" s="38"/>
       <c r="F8" s="39">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="11" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="C9" s="37">
         <v>9</v>
@@ -3471,110 +3971,120 @@
       </c>
       <c r="E9" s="38"/>
       <c r="F9" s="39">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="11" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="C10" s="37">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D10" s="37">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E10" s="38"/>
       <c r="F10" s="39">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="11" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="C11" s="37">
         <v>8</v>
       </c>
       <c r="D11" s="37">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E11" s="38"/>
       <c r="F11" s="39">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="11" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="C12" s="37">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D12" s="37">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E12" s="38"/>
       <c r="F12" s="39">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="13" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="C13" s="40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D13" s="40">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E13" s="41"/>
       <c r="F13" s="42">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="82" t="s">
-        <v>136</v>
-      </c>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="84"/>
+      <c r="A15" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" s="86" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="86" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="86" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="86" t="s">
+        <v>152</v>
+      </c>
+      <c r="F15" s="87" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="85"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="87"/>
+      <c r="A16" s="88"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="90"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="88"/>
-      <c r="B17" s="89"/>
-      <c r="C17" s="89"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="89"/>
-      <c r="F17" s="90"/>
+      <c r="A17" s="91"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3604,159 +4114,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
+      <c r="A1" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="51"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
     </row>
     <row r="4" spans="1:4" ht="15">
       <c r="A4" s="21" t="s">
-        <v>138</v>
+        <v>28</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>139</v>
+        <v>29</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>141</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="44.1" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" ht="44.1" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>147</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:4" ht="44.1" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D7" s="12"/>
     </row>
     <row r="8" spans="1:4" ht="44.1" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D8" s="12"/>
     </row>
     <row r="9" spans="1:4" ht="44.1" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="44.1" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:4" ht="44.1" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4" ht="44.1" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="D12" s="12"/>
+        <v>170</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="44.1" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="44.1" customHeight="1">
       <c r="A14" s="13" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3764,24 +4274,24 @@
     <mergeCell ref="A1:D2"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>B5="Oui"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>B5="Partiel"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>B5="Non"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="14" priority="4">
+    <cfRule type="expression" dxfId="17" priority="4">
       <formula>B5="Oui"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="5">
+    <cfRule type="expression" dxfId="16" priority="5">
       <formula>B5="Partiel"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="6">
+    <cfRule type="expression" dxfId="15" priority="6">
       <formula>B5="Non"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3806,248 +4316,238 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
+      <c r="A1" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="51"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="21" t="s">
-        <v>170</v>
+        <v>33</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>171</v>
+        <v>34</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>172</v>
+        <v>35</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>173</v>
+        <v>36</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>174</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="72" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="72" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="72" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="72" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="72" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="72" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="72" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="72" customHeight="1">
       <c r="A12" s="13" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="72" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="72" customHeight="1">
-      <c r="A14" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>215</v>
+      <c r="A14" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="72" customHeight="1">
-      <c r="A15" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>220</v>
-      </c>
+      <c r="A15" s="13"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A12">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>A5="Haute"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="13" priority="2">
       <formula>A5="Moyenne"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="12" priority="3">
       <formula>A5="Basse"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A15">
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="11" priority="4">
       <formula>A5="Haute"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="10" priority="5">
       <formula>A5="Moyenne"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>A5="Basse"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4070,379 +4570,379 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="91" t="s">
-        <v>221</v>
-      </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
+      <c r="A1" s="94" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="91"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
+      <c r="A2" s="94"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="92" t="s">
-        <v>222</v>
-      </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
+      <c r="A3" s="95" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
     </row>
     <row r="5" spans="1:7" ht="15">
       <c r="A5" s="43" t="s">
-        <v>223</v>
+        <v>40</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>224</v>
+        <v>41</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>225</v>
+        <v>42</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>226</v>
+        <v>43</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G5" s="45" t="s">
-        <v>227</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="54" customHeight="1">
       <c r="A6" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="G6" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="54" customHeight="1">
       <c r="A7" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="F7" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="F7" s="25" t="s">
+      <c r="G7" s="12" t="s">
         <v>233</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="54" customHeight="1">
       <c r="A8" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="F8" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>233</v>
-      </c>
       <c r="G8" s="12" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="54" customHeight="1">
       <c r="A9" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="F9" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>233</v>
-      </c>
       <c r="G9" s="12" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="54" customHeight="1">
       <c r="A10" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="F10" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="G10" s="12" t="s">
         <v>247</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>248</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>250</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>233</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="54" customHeight="1">
       <c r="A11" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="F11" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="B11" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="C11" s="25" t="s">
+      <c r="G11" s="12" t="s">
         <v>252</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>253</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>254</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>255</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="54" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>153</v>
+        <v>228</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="54" customHeight="1">
       <c r="A13" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>263</v>
-      </c>
       <c r="C13" s="25" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="54" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="54" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="54" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="F16" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="G16" s="12" t="s">
         <v>276</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="54" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B17" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="C17" s="25" t="s">
-        <v>282</v>
-      </c>
       <c r="D17" s="25" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>285</v>
+        <v>228</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="54" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F18" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>285</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="54" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B19" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="G19" s="14" t="s">
         <v>291</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>293</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -4451,25 +4951,794 @@
     <mergeCell ref="A3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F19">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>F6="Engagé"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>F6="Engagé provisoire"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>F6="Non engagé"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>F6="Reporté"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>F6="Partiel"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>F6="À intégrer"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="96" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="96"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="97" t="s">
+        <v>293</v>
+      </c>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>295</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>296</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="E5" s="48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="51.95" customHeight="1">
+      <c r="A6" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="51.95" customHeight="1">
+      <c r="A7" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="51.95" customHeight="1">
+      <c r="A8" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="51.95" customHeight="1">
+      <c r="A9" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="51.95" customHeight="1">
+      <c r="A10" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>317</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="51.95" customHeight="1">
+      <c r="A11" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="51.95" customHeight="1">
+      <c r="A12" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="51.95" customHeight="1">
+      <c r="A13" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="51.95" customHeight="1">
+      <c r="A14" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="51.95" customHeight="1">
+      <c r="A15" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>335</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="51.95" customHeight="1">
+      <c r="A16" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="51.95" customHeight="1">
+      <c r="A17" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>341</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>342</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>343</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E6:E17">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>E6="Fait"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="36" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="96" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="96"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+    </row>
+    <row r="4" spans="1:8" ht="15">
+      <c r="A4" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>347</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>348</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="H4" s="48" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A5" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>352</v>
+      </c>
+      <c r="D5" s="34">
+        <v>3</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A6" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="D6" s="37">
+        <v>5</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A7" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="37">
+        <v>8</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A8" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="D8" s="37">
+        <v>3</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>363</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A9" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>366</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="D9" s="37">
+        <v>3</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A10" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="D10" s="37">
+        <v>3</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A11" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="D11" s="37">
+        <v>5</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A12" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="D12" s="37">
+        <v>3</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A13" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="D13" s="37">
+        <v>5</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A14" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="D14" s="37">
+        <v>5</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A15" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="D15" s="37">
+        <v>3</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A16" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="D16" s="37">
+        <v>8</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>388</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A17" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="D17" s="37">
+        <v>5</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="45.95" customHeight="1">
+      <c r="A18" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>352</v>
+      </c>
+      <c r="D18" s="40">
+        <v>8</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>387</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>393</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15">
+      <c r="A20" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="28.5">
+      <c r="A21" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="24">
+        <v>14</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="42.75">
+      <c r="A22" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="B22" s="25">
+        <v>49</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="42.75">
+      <c r="A23" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="B23" s="25">
+        <v>18</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="28.5">
+      <c r="A24" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="B24" s="26">
+        <v>67</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>401</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:C18">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>C5="MUST"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>C5="SHOULD"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>